--- a/samples/N_其他应付款明细表.xlsx
+++ b/samples/N_其他应付款明细表.xlsx
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,16 +438,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,113 +490,346 @@
           <t>账龄(月)</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>是否关联方</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>是否函证</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>函证结果</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>重庆XX物业公司</t>
+          <t>重庆蛮好商贸有限公司</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>租赁押金</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>170000</v>
+          <t>押金</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>220000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>100000</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>8</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>已回函，无差异</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>员工代扣</t>
+          <t>重庆渝快物流有限公司</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>社保个人部分</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
+          <t>保证金</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>80000</v>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>400000</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>410000</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>90000</v>
-      </c>
       <c r="G3" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>已回函，无差异</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>重庆XX物流</t>
+          <t>重庆鑫源装备有限公司</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>运输保证金</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>100000</v>
+          <t>押金</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>120000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>280000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>140000</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>已回函，无差异</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>关联方，需在附注披露</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>重庆燃气集团</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>暂收待付</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
+          <t>代扣代缴</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>50000</v>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>340000</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>90000</v>
+      <c r="D5" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>100000</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>代缴员工燃气费</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>张三(员工)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>个人社保</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>40000</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>代扣个人社保部分</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>李四(员工)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>个人公积金</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>70000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>代扣个人公积金部分</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>重庆钢铁设备有限公司</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>质保金</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>设备质保金</t>
+        </is>
       </c>
     </row>
   </sheetData>
